--- a/practice/answers/q089.xlsx
+++ b/practice/answers/q089.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId3"/>
+    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,11 +47,22 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0024302A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0024302A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +74,18 @@
         <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,11 +93,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00A9C4AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9C4AE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9C4AE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9C4AE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9C4AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9C4AE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,7 +134,24 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22334,6 +22395,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004A7C59"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Question 36 — Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>(a)</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Variety on Rows, with Yield shown as Average and Count. All varieties remain visible.</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Among varieties with Count at least 30, SY MANNESS is highest (about 72.1) and AAC TISDALE is lowest (about 53.9).</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The minimum count removes comparisons supported by only a few reported yields.</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>The live PivotTable (and chart, where requested) is on the PivotTable worksheet. The highlighted rows there show the values used in the written answers. The Data worksheet contains the source records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A9:D10"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -96729,13 +96890,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -96743,190 +96904,196 @@
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Q89 — Variety</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2"/>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Values</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Variety</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Average of Yield_bu_ac</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Count of Yield_bu_ac</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Variety</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Average of Yield_bu_ac</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Count of Yield_bu_ac</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AAC ALIDA (BW980)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>61.41666666666666</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AAC ALIDA (BW980)</t>
+          <t>AAC BRANDON (BW 932)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>61.41666666666666</v>
+        <v>59.62215799614644</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>6</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AAC BRANDON (BW 932)</t>
+          <t>AAC BROADACRES &lt;PROVEN&gt;</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>59.62215799614644</v>
+        <v>64.98333333333333</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>519</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AAC BROADACRES &lt;PROVEN&gt;</t>
+          <t>AAC CAMERON VB &lt;CANTERRA&gt;</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>64.98333333333333</v>
+        <v>57.60526315789474</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AAC CAMERON VB &lt;CANTERRA&gt;</t>
+          <t>AAC CONNERY |PT245|</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>57.60526315789474</v>
+        <v>64.05000000000001</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AAC CONNERY |PT245|</t>
+          <t>AAC ELIE(BW931)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>64.05000000000001</v>
+        <v>59.48947368421053</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AAC ELIE(BW931)</t>
+          <t>AAC HOCKLEY |BW5044|</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>59.48947368421053</v>
+        <v>64.85254237288136</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>114</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AAC HOCKLEY |BW5044|</t>
+          <t>AAC HODGE |BW1069|</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>64.85254237288136</v>
+        <v>62.63466666666667</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>177</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AAC HODGE |BW1069|</t>
+          <t>AAC LEROY VB &lt;ALLIANCE&gt;</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>62.63466666666667</v>
+        <v>57.44657534246576</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AAC LEROY VB &lt;ALLIANCE&gt;</t>
+          <t>AAC MAGNET |BW 1045, BJ14*A01135|</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>57.44657534246576</v>
+        <v>46.76666666666667</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AAC MAGNET |BW 1045, BJ14*A01135|</t>
+          <t>AAC REDBERRY</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>46.76666666666667</v>
+        <v>54.43043478260869</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>3</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AAC REDBERRY</t>
+          <t>AAC REDSTAR &lt;SECAN&gt; |PT488|</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>54.43043478260869</v>
+        <v>57.8</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AAC REDSTAR &lt;SECAN&gt; |PT488|</t>
+          <t>AAC REDWATER (PT457)</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>57.8</v>
+        <v>42.8</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>1</v>
@@ -96935,141 +97102,141 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AAC REDWATER (PT457)</t>
+          <t>AAC SPIKE</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>42.8</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAC SPIKE</t>
+          <t>AAC STARBUCK &lt;SECAN&gt;</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>73.15000000000001</v>
+        <v>62.70320855614973</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AAC STARBUCK &lt;SECAN&gt;</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>62.70320855614973</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>374</v>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>AAC TISDALE (PT250)</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>53.86153846153846</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AAC TISDALE (PT250)</t>
+          <t>AAC VIEWFIELD &lt;FP GENETICS&gt;|BW965| EXP</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>53.86153846153846</v>
+        <v>62.47939393939394</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>39</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AAC VIEWFIELD &lt;FP GENETICS&gt;|BW965| EXP</t>
+          <t>AAC WESTKING</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>62.47939393939394</v>
+        <v>79.21764705882353</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>165</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AAC WESTKING</t>
+          <t>AAC WHEATLAND &lt;SECAN&gt;</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>79.21764705882353</v>
+        <v>65.78310502283105</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>17</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AAC WHEATLAND &lt;SECAN&gt;</t>
+          <t>AC BARRIE (BW 661)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>65.78310502283105</v>
+        <v>53.56666666666666</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>219</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AC BARRIE (BW 661)</t>
+          <t>AC CADILLAC (BW 689)</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>53.56666666666666</v>
+        <v>47.3</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AC CADILLAC (BW 689)</t>
+          <t>AC DOMAIN (BW 148)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>47.3</v>
+        <v>37.63333333333333</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AC DOMAIN (BW 148)</t>
+          <t>AC SPLENDOR (BW 191)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>37.63333333333333</v>
+        <v>27</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AC SPLENDOR (BW 191)</t>
+          <t>AC STETTLER &lt;SECAN&gt; |BW867|</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>1</v>
@@ -97078,286 +97245,273 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AC STETTLER &lt;SECAN&gt; |BW867|</t>
+          <t>BOLLES &lt;SEED DEPOT&gt;</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>59</v>
+        <v>58.1378640776699</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BOLLES &lt;SEED DEPOT&gt;</t>
+          <t>CARBERRY (BW874)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>58.1378640776699</v>
+        <v>49.175</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>103</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CARBERRY (BW874)</t>
+          <t>CARDALE (BW429)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>49.175</v>
+        <v>55.9125</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CARDALE (BW429)</t>
+          <t>CDC ENVY</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>55.9125</v>
+        <v>63</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDC ENVY</t>
+          <t>CDC GO (BW781)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>63</v>
+        <v>77.5</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDC GO (BW781)</t>
+          <t>CDC HUGHES &lt;CPSC&gt; |PT588|</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>77.5</v>
+        <v>53.58</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDC HUGHES &lt;CPSC&gt; |PT588|</t>
+          <t>CDC IMAGINE (BW758)(IMI)</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>53.58</v>
+        <v>62.9</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CDC IMAGINE (BW758)(IMI)</t>
+          <t>CDC LANDMARK</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>62.9</v>
+        <v>60.73333333333333</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CDC LANDMARK</t>
+          <t>CDC ORTONA &lt;PROVEN&gt;</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>60.73333333333333</v>
+        <v>59.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDC ORTONA &lt;PROVEN&gt;</t>
+          <t>CDC PLENTIFUL (PT580)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>59.5</v>
+        <v>55.80769230769231</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDC PLENTIFUL (PT580)</t>
+          <t>CDC SKRUSH |PT599|</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>55.80769230769231</v>
+        <v>60.5</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDC SKRUSH |PT599|</t>
+          <t>CDC STANLEY (BW880)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>60.5</v>
+        <v>47.25714285714286</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CDC STANLEY (BW880)</t>
+          <t>CS DAYBREAK &lt;CANTERRA&gt;</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>47.25714285714286</v>
+        <v>52.77</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CS DAYBREAK &lt;CANTERRA&gt;</t>
+          <t>GLENN</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>52.77</v>
+        <v>64.47499999999999</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GLENN</t>
+          <t>HARVEST (BW259)</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>64.47499999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HARVEST (BW259)</t>
+          <t>SHELLY</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>64.40000000000001</v>
+        <v>51.95</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHELLY</t>
+          <t>SY CAST</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>51.95</v>
+        <v>59.51000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SY CAST</t>
+          <t>SY GABBRO &lt;SYNGENTA&gt;</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>59.51000000000001</v>
+        <v>56.24210526315789</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SY GABBRO &lt;SYNGENTA&gt;</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>56.24210526315789</v>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>19</v>
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>SY MANNESS</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>72.12129629629629</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SY MANNESS</t>
+          <t>SY TORACH &lt;SYNGENTA&gt;</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>72.12129629629629</v>
+        <v>53.46153846153846</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>108</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SY TORACH &lt;SYNGENTA&gt;</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>53.46153846153846</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B50" s="8" t="n">
+      <c r="B49" s="8" t="n">
         <v>61.15617180984153</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C49" s="9" t="n">
         <v>2398</v>
       </c>
     </row>
